--- a/service_texts_generator2_3CZ1_0.xlsx
+++ b/service_texts_generator2_3CZ1_0.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eichler536\github\VDV301tester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9494913-06D0-4FBF-B5EE-848A57B6EC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EFC6A1-9AE6-4A5E-AAA6-5F2228155975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Namluvit" sheetId="5" r:id="rId1"/>
     <sheet name="slozit" sheetId="8" r:id="rId2"/>
-    <sheet name="List1" sheetId="10" r:id="rId3"/>
+    <sheet name="mergedResult" sheetId="10" r:id="rId3"/>
     <sheet name="Namluveno k 12-2020" sheetId="7" r:id="rId4"/>
     <sheet name="ciselnik" sheetId="9" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="612">
   <si>
     <t>OIS</t>
   </si>
@@ -1635,27 +1635,15 @@
     <t>Funkčnost klimatizace</t>
   </si>
   <si>
-    <t>Potraviny</t>
-  </si>
-  <si>
     <t>Nastupujte předními dveřmi</t>
   </si>
   <si>
-    <t>Nepokládat zavazadla</t>
-  </si>
-  <si>
     <t>Neprůjezdnost, linka ukončena</t>
   </si>
   <si>
     <t>Neprůjezdnost, odklon</t>
   </si>
   <si>
-    <t>Prostor pro invalidní vozík</t>
-  </si>
-  <si>
-    <t>Prostor pro kočárek</t>
-  </si>
-  <si>
     <t>Přední dveře, předložte doklad</t>
   </si>
   <si>
@@ -1665,18 +1653,6 @@
     <t>Vozidlo obsazeno</t>
   </si>
   <si>
-    <t>Vyčkáváme na vzájemný přestup</t>
-  </si>
-  <si>
-    <t>Silná IAD, odklon</t>
-  </si>
-  <si>
-    <t>zpoždění IAD</t>
-  </si>
-  <si>
-    <t>postupte dále</t>
-  </si>
-  <si>
     <t>Air</t>
   </si>
   <si>
@@ -1750,9 +1726,6 @@
   </si>
   <si>
     <t>displayName</t>
-  </si>
-  <si>
-    <t>komplet</t>
   </si>
   <si>
     <t>&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
@@ -1855,22 +1828,147 @@
     <t>XS2</t>
   </si>
   <si>
-    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+    <t>zkrácený spoj DEMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  </t>
+  </si>
+  <si>
+    <t>info o výluce DEMO</t>
+  </si>
+  <si>
+    <t>&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>trvalá změna DEMO</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
+autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
+na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;
+From saturday, &amp;lt;b&amp;gt;the 1st September 2018&amp;lt;/b&amp;gt;, several permanent changes and modifications
+will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
+information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>Jiné sdělení DEMO</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
+na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
+&amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
+s dostatečným předstihem &amp;lt;b&amp;gt;tlačítko STOP&amp;lt;/b&amp;gt; nebo tlačítko pro
+otevření dveří. Další informace naleznete na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;From saturday, the 1st July 2019, buses on all stops at Prague will stop on request only.
+You don‘t have lift a hand to stop the bus, &amp;lt;b&amp;gt;just stand in the bus stop area&amp;lt;/b&amp;gt;. Press the
+&amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;</t>
+  </si>
+  <si>
+    <t>Postupujte dále do vozu</t>
+  </si>
+  <si>
+    <t>Invalidní vozík</t>
+  </si>
+  <si>
+    <t>Kočárek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zákaz jídla a pití </t>
+  </si>
+  <si>
+    <t>Zavazadla</t>
+  </si>
+  <si>
+    <t>Vzájemný přestup</t>
+  </si>
+  <si>
+    <t>Vyčkávání na čas odjezdu</t>
+  </si>
+  <si>
+    <t>&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;</t>
+  </si>
+  <si>
+    <t>Vzájemný přestup (vlak)</t>
+  </si>
+  <si>
+    <t>Letiště DEMO</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí mimo Schengenský prostor &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to countries outside the Schengen Area&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí Schengenského prostoru &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to Schengen Area countries&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
+departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>Odklon</t>
+  </si>
+  <si>
+    <t>Zpoždění</t>
+  </si>
+  <si>
+    <t>Zpráva z dispečinku DEMO</t>
+  </si>
+  <si>
+    <t>&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
+    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
+    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
+    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
+    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
+    na metro „A“).&amp;lt;br&amp;gt;
+    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
+    komunikací (během dnešního odpoledne).
+&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+    &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
+&amp;lt;/color&amp;gt;    </t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;</t>
-  </si>
-  <si>
-    <t>Čas odjezdu dle JŘ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1961,6 +2059,14 @@
       <name val="Alwyn New Rg"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2041,7 +2147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2087,25 +2193,30 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Normální 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -4207,12 +4318,12 @@
   </sheetData>
   <autoFilter ref="A1:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="containsBlanks" dxfId="21" priority="121" stopIfTrue="1">
+    <cfRule type="containsBlanks" dxfId="20" priority="121" stopIfTrue="1">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B178">
-    <cfRule type="duplicateValues" dxfId="20" priority="122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="122" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="74" fitToHeight="7" orientation="portrait" r:id="rId1"/>
@@ -4221,39 +4332,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="6" width="43.42578125" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.5703125" customWidth="1"/>
-    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="7" width="43.42578125" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.5703125" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="D1" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>522</v>
@@ -4267,893 +4378,766 @@
       <c r="K1" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="W1" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" t="s">
-        <v>453</v>
-      </c>
-      <c r="M2" t="str">
+      <c r="L1" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="207" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>593</v>
+      </c>
+      <c r="B2" s="24">
+        <v>5</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>558</v>
+      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" t="s">
+        <v>406</v>
+      </c>
+      <c r="N2" t="str">
         <f>CONCATENATE("&lt;",A$1,"&gt;",A2,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;</v>
-      </c>
-      <c r="N2" t="str">
+        <v>&lt;displayName&gt;Zavazadla&lt;/displayName&gt;</v>
+      </c>
+      <c r="O2" t="str">
         <f>CONCATENATE("&lt;",B$1,"&gt;",B2,"&lt;/",B$1,"&gt;")</f>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P2" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C2,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O2" t="str">
-        <f>CONCATENATE("&lt;",C$1,"&gt;",C2,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <f>CONCATENATE("&lt;",D$1,"&gt;",D2,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;</v>
-      </c>
-      <c r="Q2" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R2" t="str">
         <f>CONCATENATE("&lt;",E$1,"&gt;",E2,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
+zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S2" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F2,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R2" t="str">
-        <f>CONCATENATE("&lt;",F$1,"&gt;",F2,"&lt;/",F$1,"&gt;")</f>
+      <c r="T2" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G2,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S2" t="str">
-        <f>IF(G2&lt;&gt;"",CONCATENATE("&lt;",G$1,"&gt;",G2,".mp3","&lt;/",G$1,"&gt;"),"")</f>
-        <v>&lt;mp3&gt;H350.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T2" t="str">
+      <c r="U2" t="str">
         <f>IF(H2&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H2,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U2" t="str">
+        <v>&lt;mp3&gt;H239.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V2" t="str">
         <f>IF(I2&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I2,".mp3","&lt;/",I$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="V2" t="str">
+      <c r="W2" t="str">
         <f>IF(J2&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J2,".mp3","&lt;/",J$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="W2" t="str">
-        <f>CONCATENATE("&lt;announcement&gt;",M2,N2,O2,P2,Q2,R2,S2,T2,U2,V2,"&lt;/announcement&gt;")</f>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="207" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>524</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>564</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="E3" s="20"/>
+      <c r="X2" t="str">
+        <f>IF(K2&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K2,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <f>CONCATENATE("&lt;announcement&gt;",N2,O2,P2,Q2,R2,S2,T2,U2,V2,W2,X2,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Zavazadla&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
+zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="207" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="B3" s="24">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>556</v>
+      </c>
       <c r="F3" s="20"/>
-      <c r="G3" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" t="s">
         <v>451</v>
       </c>
-      <c r="M3" t="str">
-        <f t="shared" ref="M3:M19" si="0">CONCATENATE("&lt;",A$1,"&gt;",A3,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;Potraviny&lt;/displayName&gt;</v>
-      </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N17" si="1">CONCATENATE("&lt;",B$1,"&gt;",B3,"&lt;/",B$1,"&gt;")</f>
+        <f t="shared" ref="N3:N8" si="0">CONCATENATE("&lt;",A$1,"&gt;",A3,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O26" si="1">CONCATENATE("&lt;",B$1,"&gt;",B3,"&lt;/",B$1,"&gt;")</f>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P8" si="2">CONCATENATE("&lt;",C$1,"&gt;",C3,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O3" t="str">
-        <f t="shared" ref="O3:O17" si="2">CONCATENATE("&lt;",C$1,"&gt;",C3,"&lt;/",C$1,"&gt;")</f>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q8" si="3">CONCATENATE("&lt;",D$1,"&gt;",D3,"&lt;/",D$1,"&gt;")</f>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="P3" t="str">
-        <f t="shared" ref="P3:P17" si="3">CONCATENATE("&lt;",D$1,"&gt;",D3,"&lt;/",D$1,"&gt;")</f>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R8" si="4">CONCATENATE("&lt;",E$1,"&gt;",E3,"&lt;/",E$1,"&gt;")</f>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
 potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q19" si="4">CONCATENATE("&lt;",E$1,"&gt;",E3,"&lt;/",E$1,"&gt;")</f>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S8" si="5">CONCATENATE("&lt;",F$1,"&gt;",F3,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R3" t="str">
-        <f t="shared" ref="R3:R19" si="5">CONCATENATE("&lt;",F$1,"&gt;",F3,"&lt;/",F$1,"&gt;")</f>
+      <c r="T3" t="str">
+        <f t="shared" ref="T3:T8" si="6">CONCATENATE("&lt;",G$1,"&gt;",G3,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S3" t="str">
-        <f t="shared" ref="S3:S17" si="6">IF(G3&lt;&gt;"",CONCATENATE("&lt;",G$1,"&gt;",G3,".mp3","&lt;/",G$1,"&gt;"),"")</f>
+      <c r="U3" t="str">
+        <f t="shared" ref="U3:U8" si="7">IF(H3&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H3,".mp3","&lt;/",H$1,"&gt;"),"")</f>
         <v>&lt;mp3&gt;H340.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="T3" t="str">
-        <f>IF(H3&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H3,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U3" t="str">
+      <c r="V3" t="str">
         <f>IF(I3&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I3,".mp3","&lt;/",I$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="V3" t="str">
+      <c r="W3" t="str">
         <f>IF(J3&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J3,".mp3","&lt;/",J$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="W3" t="str">
-        <f t="shared" ref="W3:W19" si="7">CONCATENATE("&lt;announcement&gt;",M3,N3,O3,P3,Q3,R3,S3,T3,U3,V3,"&lt;/announcement&gt;")</f>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Potraviny&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
+      <c r="X3" t="str">
+        <f>IF(K3&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K3,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <f t="shared" ref="Y3:Y26" si="8">CONCATENATE("&lt;announcement&gt;",N3,O3,P3,Q3,R3,S3,T3,U3,V3,W3,X3,"&lt;/announcement&gt;")</f>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
 potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>525</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" t="s">
-        <v>348</v>
-      </c>
-      <c r="M4" t="str">
+    <row r="4" spans="1:25" ht="207" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="B4" s="24">
+        <v>5</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;</v>
-      </c>
-      <c r="N4" t="str">
+        <v>&lt;displayName&gt;Kočárek&lt;/displayName&gt;</v>
+      </c>
+      <c r="O4" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R4" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
+místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T4" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U4" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H240.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V4" t="str">
+        <f>IF(I4&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I4,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <f>IF(J4&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J4,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <f>IF(K4&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K4,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Kočárek&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
+místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="207" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="B5" s="24">
+        <v>5</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" t="s">
+        <v>415</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P5" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P4" t="str">
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q5" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;</v>
-      </c>
-      <c r="Q4" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R5" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R4" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S4" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H205.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T4" t="str">
-        <f>IF(H4&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H4,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <f>IF(I4&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I4,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <f>IF(J4&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J4,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="207" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>526</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>566</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" t="s">
-        <v>406</v>
-      </c>
-      <c r="M5" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Nepokládat zavazadla&lt;/displayName&gt;</v>
-      </c>
-      <c r="N5" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O5" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P5" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R5" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S5" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H239.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T5" t="str">
-        <f>IF(H5&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H5,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <f>IF(I5&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I5,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <f>IF(J5&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J5,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Nepokládat zavazadla&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" t="s">
-        <v>281</v>
-      </c>
-      <c r="M6" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;</v>
-      </c>
-      <c r="N6" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O6" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P6" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;</v>
-      </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R6" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S6" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H162.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T6" t="str">
-        <f>IF(H6&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H6,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U6" t="str">
-        <f>IF(I6&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I6,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V6" t="str">
-        <f>IF(J6&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J6,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W6" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="60" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>528</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>568</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" t="s">
-        <v>285</v>
-      </c>
-      <c r="M7" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;</v>
-      </c>
-      <c r="N7" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O7" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P7" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;</v>
-      </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R7" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S7" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H164.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T7" t="str">
-        <f>IF(H7&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H7,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U7" t="str">
-        <f>IF(I7&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I7,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V7" t="str">
-        <f>IF(J7&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J7,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="207" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>529</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" t="s">
-        <v>415</v>
-      </c>
-      <c r="M8" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Prostor pro invalidní vozík&lt;/displayName&gt;</v>
-      </c>
-      <c r="N8" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O8" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P8" t="str">
-        <f t="shared" si="3"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
 místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="4"/>
+      <c r="S5" t="str">
+        <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R8" t="str">
-        <f t="shared" si="5"/>
+      <c r="T5" t="str">
+        <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S8" t="str">
-        <f t="shared" si="6"/>
+      <c r="U5" t="str">
+        <f t="shared" si="7"/>
         <v>&lt;mp3&gt;H260.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="T8" t="str">
-        <f>IF(H8&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H8,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U8" t="str">
-        <f>IF(I8&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I8,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V8" t="str">
-        <f>IF(J8&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J8,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Prostor pro invalidní vozík&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
+      <c r="V5" t="str">
+        <f>IF(I5&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I5,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <f>IF(J5&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J5,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <f>IF(K5&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K5,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
 místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="207" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C9" s="17" t="s">
+    <row r="6" spans="1:25" ht="224.25" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" s="24">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>572</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" t="s">
-        <v>408</v>
-      </c>
-      <c r="M9" t="str">
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" t="s">
+        <v>309</v>
+      </c>
+      <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Prostor pro kočárek&lt;/displayName&gt;</v>
-      </c>
-      <c r="N9" t="str">
+        <v>&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;</v>
+      </c>
+      <c r="O6" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O9" t="str">
+      <c r="Q6" t="str">
+        <f t="shared" si="3"/>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
+          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
+          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="5"/>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T6" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="7"/>
+        <v>&lt;mp3&gt;H179.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V6" t="str">
+        <f>IF(I6&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I6,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <f>IF(J6&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J6,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <f>IF(K6&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K6,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
+          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
+          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="189.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="B7" s="24">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" t="s">
+        <v>423</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P7" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P9" t="str">
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q7" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="Q9" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R7" t="str">
         <f t="shared" si="4"/>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
+dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
+departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R9" t="str">
-        <f t="shared" si="5"/>
+      <c r="T7" t="str">
+        <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S9" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H240.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T9" t="str">
-        <f>IF(H9&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H9,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U9" t="str">
-        <f>IF(I9&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I9,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V9" t="str">
-        <f>IF(J9&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J9,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W9" t="str">
+      <c r="U7" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Prostor pro kočárek&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>531</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="M10" t="str">
+        <v>&lt;mp3&gt;H281.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V7" t="str">
+        <f>IF(I7&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I7,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <f>IF(J7&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J7,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <f>IF(K7&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K7,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
+dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
+departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="155.25" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="B8" s="24">
+        <v>5</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" t="s">
+        <v>428</v>
+      </c>
+      <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;</v>
-      </c>
-      <c r="N10" t="str">
+        <v>&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;</v>
+      </c>
+      <c r="O8" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="2"/>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O10" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P10" t="str">
+      <c r="Q8" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;</v>
-      </c>
-      <c r="Q10" t="str">
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R8" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R10" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H183.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T10" t="str">
-        <f>IF(H10&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H10,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <f>IF(I10&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I10,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <f>IF(J10&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J10,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>532</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" t="s">
-        <v>315</v>
-      </c>
-      <c r="M11" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;</v>
-      </c>
-      <c r="N11" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O11" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P11" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;</v>
-      </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R11" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S11" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H182.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T11" t="str">
-        <f>IF(H11&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H11,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U11" t="str">
-        <f>IF(I11&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I11,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V11" t="str">
-        <f>IF(J11&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J11,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W11" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>533</v>
-      </c>
-      <c r="C12" t="s">
-        <v>546</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" t="s">
-        <v>340</v>
-      </c>
-      <c r="M12" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;</v>
-      </c>
-      <c r="N12" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O12" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;Info&lt;/icon&gt;</v>
-      </c>
-      <c r="P12" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;</v>
-      </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="4"/>
-        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R12" t="str">
-        <f t="shared" si="5"/>
-        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S12" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H201.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T12" t="str">
-        <f>IF(H12&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H12,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U12" t="str">
-        <f>IF(I12&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I12,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V12" t="str">
-        <f>IF(J12&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J12,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W12" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;Info&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="155.25" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>534</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" t="s">
-        <v>428</v>
-      </c>
-      <c r="M13" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Vyčkáváme na vzájemný přestup&lt;/displayName&gt;</v>
-      </c>
-      <c r="N13" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;type&gt;&lt;/type&gt;</v>
-      </c>
-      <c r="O13" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P13" t="str">
-        <f t="shared" si="3"/>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="4"/>
+      <c r="S8" t="str">
+        <f t="shared" si="5"/>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R13" t="str">
-        <f t="shared" si="5"/>
+      <c r="T8" t="str">
+        <f t="shared" si="6"/>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S13" t="str">
-        <f t="shared" si="6"/>
+      <c r="U8" t="str">
+        <f t="shared" si="7"/>
         <v>&lt;mp3&gt;H284.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="T13" t="str">
-        <f>IF(H13&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H13,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U13" t="str">
-        <f>IF(I13&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I13,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V13" t="str">
-        <f>IF(J13&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J13,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na vzájemný přestup&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+      <c r="V8" t="str">
+        <f>IF(I8&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I8,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <f>IF(J8&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J8,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <f>IF(K8&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K8,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="258.75" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>535</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>568</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" t="s">
+    <row r="9" spans="1:25" ht="172.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="B9" s="24">
+        <v>5</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>598</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="N9" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A9,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P9" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C9,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q9" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D9,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R9" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E9,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S9" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F9,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T9" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G9,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U9" t="str">
+        <f>IF(H9&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H9,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <f>IF(I9&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I9,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <f>IF(J9&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J9,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <f>IF(K9&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K9,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="167.25" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="B10" s="24">
+        <v>5</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" t="s">
         <v>419</v>
       </c>
-      <c r="M14" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Silná IAD, odklon&lt;/displayName&gt;</v>
-      </c>
-      <c r="N14" t="str">
+      <c r="N10" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A10,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Odklon&lt;/displayName&gt;</v>
+      </c>
+      <c r="O10" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P10" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C10,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O14" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P14" t="str">
-        <f t="shared" si="3"/>
+      <c r="Q10" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D10,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R10" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E10,"&lt;/",E$1,"&gt;")</f>
         <v>&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
 pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
 &amp;lt;/color&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="4"/>
+      <c r="S10" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F10,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R14" t="str">
-        <f t="shared" si="5"/>
+      <c r="T10" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G10,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S14" t="str">
-        <f t="shared" si="6"/>
+      <c r="U10" t="str">
+        <f>IF(H10&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H10,".mp3","&lt;/",H$1,"&gt;"),"")</f>
         <v>&lt;mp3&gt;H279.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="T14" t="str">
-        <f>IF(H14&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H14,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U14" t="str">
-        <f>IF(I14&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I14,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <f>IF(J14&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J14,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Silná IAD, odklon&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+      <c r="V10" t="str">
+        <f>IF(I10&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I10,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <f>IF(J10&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J10,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <f>IF(K10&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K10,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
 pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
 &amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H279.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="189.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>576</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" t="s">
-        <v>423</v>
-      </c>
-      <c r="M15" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;Čas odjezdu dle JŘ&lt;/displayName&gt;</v>
-      </c>
-      <c r="N15" t="str">
+    <row r="11" spans="1:25" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
+        <v>600</v>
+      </c>
+      <c r="B11" s="24">
+        <v>5</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>602</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="N11" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A11,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O11" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P11" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C11,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O15" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P15" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="4"/>
+      <c r="Q11" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D11,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
+departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R11" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E11,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí mimo Schengenský prostor &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to countries outside the Schengen Area&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí Schengenského prostoru &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to Schengen Area countries&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S11" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F11,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R15" t="str">
-        <f t="shared" si="5"/>
+      <c r="T11" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G11,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S15" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H281.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T15" t="str">
-        <f>IF(H15&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H15,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <f>IF(I15&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I15,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <f>IF(J15&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J15,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;Čas odjezdu dle JŘ&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="293.25" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>536</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" t="s">
+      <c r="U11" t="str">
+        <f>IF(H11&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H11,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <f>IF(I11&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I11,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <f>IF(J11&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J11,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <f>IF(K11&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K11,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
+departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí mimo Schengenský prostor &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to countries outside the Schengen Area&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí Schengenského prostoru &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to Schengen Area countries&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="293.25" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>604</v>
+      </c>
+      <c r="B12" s="24">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" t="s">
         <v>421</v>
       </c>
-      <c r="M16" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;zpoždění IAD&lt;/displayName&gt;</v>
-      </c>
-      <c r="N16" t="str">
+      <c r="N12" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A12,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Zpoždění&lt;/displayName&gt;</v>
+      </c>
+      <c r="O12" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P12" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C12,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O16" t="str">
-        <f t="shared" si="2"/>
+      <c r="Q12" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D12,"&lt;/",D$1,"&gt;")</f>
         <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
-      <c r="P16" t="str">
-        <f t="shared" si="3"/>
+      <c r="R12" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E12,"&lt;/",E$1,"&gt;")</f>
         <v>&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
           se za zpoždění linky,
           které je zapříčiněno silnou individiální
@@ -5162,33 +5146,33 @@
           caused by heavy traffic and
           limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="4"/>
+      <c r="S12" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F12,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R16" t="str">
-        <f t="shared" si="5"/>
+      <c r="T12" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G12,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S16" t="str">
-        <f t="shared" si="6"/>
+      <c r="U12" t="str">
+        <f>IF(H12&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H12,".mp3","&lt;/",H$1,"&gt;"),"")</f>
         <v>&lt;mp3&gt;H280.mp3&lt;/mp3&gt;</v>
       </c>
-      <c r="T16" t="str">
-        <f>IF(H16&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H16,".mp3","&lt;/",H$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="U16" t="str">
-        <f>IF(I16&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I16,".mp3","&lt;/",I$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <f>IF(J16&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J16,".mp3","&lt;/",J$1,"&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;zpoždění IAD&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
+      <c r="V12" t="str">
+        <f>IF(I12&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I12,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <f>IF(J12&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J12,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <f>IF(K12&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K12,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Zpoždění&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
           se za zpoždění linky,
           které je zapříčiněno silnou individiální
           dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
@@ -5197,222 +5181,1025 @@
           limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="224.25" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>537</v>
-      </c>
-      <c r="C17" s="3" t="s">
+    <row r="13" spans="1:25" ht="102" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B13" s="24">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="F13">
+        <v>6.8</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7</v>
+      </c>
+      <c r="N13" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A13,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
+      </c>
+      <c r="P13" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C13,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;FareZoneChange&lt;/type&gt;</v>
+      </c>
+      <c r="Q13" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D13,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R13" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E13,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S13" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F13,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T13" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G13,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;7&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U13" t="str">
+        <f>IF(H13&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H13,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <f>IF(I13&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I13,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f>IF(J13&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J13,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <f>IF(K13&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K13,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B14" s="24">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="F14">
+        <v>123</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="N14" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A14,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;10&lt;/duration&gt;</v>
+      </c>
+      <c r="P14" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C14,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;LineChange&lt;/type&gt;</v>
+      </c>
+      <c r="Q14" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D14,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R14" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E14,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S14" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F14,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;123&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T14" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G14,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;XS2&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U14" t="str">
+        <f>IF(H14&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H14,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <f>IF(I14&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I14,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f>IF(J14&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J14,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <f>IF(K14&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K14,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" t="s">
-        <v>309</v>
-      </c>
-      <c r="M17" t="str">
-        <f t="shared" si="0"/>
-        <v>&lt;displayName&gt;postupte dále&lt;/displayName&gt;</v>
+      <c r="B15" s="24">
+        <v>5</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="N15" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A15,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P15" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C15,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q15" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D15,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R15" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E15,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;</v>
+      </c>
+      <c r="S15" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F15,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T15" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G15,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U15" t="str">
+        <f>IF(H15&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H15,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <f>IF(I15&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I15,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <f>IF(J15&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J15,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <f>IF(K15&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K15,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B16" s="24">
+        <v>5</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>559</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="N16" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A16,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P16" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C16,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q16" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D16,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R16" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E16,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S16" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F16,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T16" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G16,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U16" t="str">
+        <f>IF(H16&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H16,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <f>IF(I16&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I16,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <f>IF(J16&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J16,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <f>IF(K16&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K16,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="255" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B17" s="24">
+        <v>5</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>585</v>
       </c>
       <c r="N17" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A17,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O17" t="str">
         <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P17" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C17,"&lt;/",C$1,"&gt;")</f>
         <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
-      <c r="O17" t="str">
-        <f t="shared" si="2"/>
-        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P17" t="str">
-        <f t="shared" si="3"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
       <c r="Q17" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D17,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R17" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E17,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
+autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
+na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;
+From saturday, &amp;lt;b&amp;gt;the 1st September 2018&amp;lt;/b&amp;gt;, several permanent changes and modifications
+will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
+information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S17" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F17,"&lt;/",F$1,"&gt;")</f>
         <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
       </c>
-      <c r="R17" t="str">
-        <f t="shared" si="5"/>
+      <c r="T17" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G17,"&lt;/",G$1,"&gt;")</f>
         <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
       </c>
-      <c r="S17" t="str">
-        <f t="shared" si="6"/>
-        <v>&lt;mp3&gt;H179.mp3&lt;/mp3&gt;</v>
-      </c>
-      <c r="T17" t="str">
+      <c r="U17" t="str">
         <f>IF(H17&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H17,".mp3","&lt;/",H$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="U17" t="str">
+      <c r="V17" t="str">
         <f>IF(I17&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I17,".mp3","&lt;/",I$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="V17" t="str">
+      <c r="W17" t="str">
         <f>IF(J17&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J17,".mp3","&lt;/",J$1,"&gt;"),"")</f>
         <v/>
       </c>
-      <c r="W17" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;postupte dále&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="X17" t="str">
+        <f>IF(K17&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K17,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
+autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
+na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;
+From saturday, &amp;lt;b&amp;gt;the 1st September 2018&amp;lt;/b&amp;gt;, several permanent changes and modifications
+will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
+information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="344.25" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="B18" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>589</v>
-      </c>
-      <c r="E18">
-        <v>6.8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>7</v>
-      </c>
-      <c r="M18" t="str">
-        <f t="shared" ref="M18:M19" si="8">CONCATENATE("&lt;",A$1,"&gt;",A18,"&lt;/",A$1,"&gt;")</f>
-        <v>&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;</v>
+      <c r="B18" s="24">
+        <v>5</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>587</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" ref="N18:N19" si="9">CONCATENATE("&lt;",B$1,"&gt;",B18,"&lt;/",B$1,"&gt;")</f>
-        <v>&lt;type&gt;FareZoneChange&lt;/type&gt;</v>
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A18,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;</v>
       </c>
       <c r="O18" t="str">
-        <f t="shared" ref="O18:O19" si="10">CONCATENATE("&lt;",C$1,"&gt;",C18,"&lt;/",C$1,"&gt;")</f>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
       </c>
       <c r="P18" t="str">
-        <f t="shared" ref="P18:P19" si="11">CONCATENATE("&lt;",D$1,"&gt;",D18,"&lt;/",D$1,"&gt;")</f>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C18,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
       </c>
       <c r="Q18" t="str">
-        <f t="shared" ref="Q18:Q19" si="12">CONCATENATE("&lt;",E$1,"&gt;",E18,"&lt;/",E$1,"&gt;")</f>
-        <v>&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;</v>
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D18,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
       </c>
       <c r="R18" t="str">
-        <f t="shared" ref="R18:R19" si="13">CONCATENATE("&lt;",F$1,"&gt;",F18,"&lt;/",F$1,"&gt;")</f>
-        <v>&lt;changeTo&gt;7&lt;/changeTo&gt;</v>
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E18,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
+na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
+&amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
+s dostatečným předstihem &amp;lt;b&amp;gt;tlačítko STOP&amp;lt;/b&amp;gt; nebo tlačítko pro
+otevření dveří. Další informace naleznete na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;From saturday, the 1st July 2019, buses on all stops at Prague will stop on request only.
+You don‘t have lift a hand to stop the bus, &amp;lt;b&amp;gt;just stand in the bus stop area&amp;lt;/b&amp;gt;. Press the
+&amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
       </c>
       <c r="S18" t="str">
-        <f t="shared" ref="S18:S19" si="14">IF(G18&lt;&gt;"",CONCATENATE("&lt;",G$1,"&gt;",G18,".mp3","&lt;/",G$1,"&gt;"),"")</f>
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F18,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T18" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G18,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U18" t="str">
+        <f>IF(H18&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H18,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V18" t="str">
+        <f>IF(I18&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I18,".mp3","&lt;/",I$1,"&gt;"),"")</f>
         <v/>
       </c>
       <c r="W18" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="76.5" x14ac:dyDescent="0.2">
+        <f>IF(J18&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J18,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <f>IF(K18&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K18,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
+na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
+&amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
+s dostatečným předstihem &amp;lt;b&amp;gt;tlačítko STOP&amp;lt;/b&amp;gt; nebo tlačítko pro
+otevření dveří. Další informace naleznete na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;From saturday, the 1st July 2019, buses on all stops at Prague will stop on request only.
+You don‘t have lift a hand to stop the bus, &amp;lt;b&amp;gt;just stand in the bus stop area&amp;lt;/b&amp;gt;. Press the
+&amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="216.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>590</v>
-      </c>
-      <c r="E19">
-        <v>123</v>
-      </c>
-      <c r="F19" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B19" s="24">
+        <v>15</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="N19" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A19,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Zpráva z dispečinku DEMO&lt;/displayName&gt;</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;15&lt;/duration&gt;</v>
+      </c>
+      <c r="P19" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C19,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q19" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D19,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+    &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
+&amp;lt;/color&amp;gt;    &lt;/icon&gt;</v>
+      </c>
+      <c r="R19" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E19,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
+    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
+    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
+    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
+    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
+    na metro „A“).&amp;lt;br&amp;gt;
+    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
+    komunikací (během dnešního odpoledne).
+&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;</v>
+      </c>
+      <c r="S19" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F19,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T19" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G19,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U19" t="str">
+        <f>IF(H19&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H19,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="V19" t="str">
+        <f>IF(I19&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I19,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <f>IF(J19&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J19,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <f>IF(K19&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K19,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Zpráva z dispečinku DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+    &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
+&amp;lt;/color&amp;gt;    &lt;/icon&gt;&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
+    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
+    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
+    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
+    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
+    na metro „A“).&amp;lt;br&amp;gt;
+    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
+    komunikací (během dnešního odpoledne).
+&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>523</v>
+      </c>
+      <c r="B20" s="24">
+        <v>5</v>
+      </c>
+      <c r="D20" s="23" t="s">
         <v>588</v>
       </c>
-      <c r="M19" t="str">
+      <c r="E20" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" t="s">
+        <v>453</v>
+      </c>
+      <c r="N20" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A20,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P20" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C20,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q20" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D20,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R20" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E20,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;</v>
+      </c>
+      <c r="S20" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F20,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T20" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G20,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U20" t="str">
+        <f>IF(H20&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H20,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H350.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V20" t="str">
+        <f>IF(I20&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I20,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <f>IF(J20&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J20,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <f>IF(K20&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K20,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y20" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;</v>
-      </c>
-      <c r="N19" t="str">
-        <f t="shared" si="9"/>
-        <v>&lt;type&gt;LineChange&lt;/type&gt;</v>
-      </c>
-      <c r="O19" t="str">
-        <f t="shared" si="10"/>
-        <v>&lt;icon&gt;&lt;/icon&gt;</v>
-      </c>
-      <c r="P19" t="str">
-        <f t="shared" si="11"/>
-        <v>&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;</v>
-      </c>
-      <c r="Q19" t="str">
-        <f t="shared" si="12"/>
-        <v>&lt;changeFrom&gt;123&lt;/changeFrom&gt;</v>
-      </c>
-      <c r="R19" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;changeTo&gt;XS2&lt;/changeTo&gt;</v>
-      </c>
-      <c r="S19" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="W19" t="str">
-        <f t="shared" si="7"/>
-        <v>&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;</v>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>524</v>
+      </c>
+      <c r="B21" s="24">
+        <v>5</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" t="s">
+        <v>348</v>
+      </c>
+      <c r="N21" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A21,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P21" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C21,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q21" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D21,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R21" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E21,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;</v>
+      </c>
+      <c r="S21" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F21,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T21" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G21,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U21" t="str">
+        <f>IF(H21&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H21,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H205.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V21" t="str">
+        <f>IF(I21&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I21,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <f>IF(J21&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J21,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <f>IF(K21&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K21,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>525</v>
+      </c>
+      <c r="B22" s="24">
+        <v>5</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" t="s">
+        <v>281</v>
+      </c>
+      <c r="N22" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A22,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;</v>
+      </c>
+      <c r="O22" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P22" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C22,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q22" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D22,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R22" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E22,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;</v>
+      </c>
+      <c r="S22" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F22,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T22" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G22,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U22" t="str">
+        <f>IF(H22&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H22,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H162.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V22" t="str">
+        <f>IF(I22&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I22,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <f>IF(J22&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J22,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <f>IF(K22&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K22,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="60" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>526</v>
+      </c>
+      <c r="B23" s="24">
+        <v>5</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" t="s">
+        <v>285</v>
+      </c>
+      <c r="N23" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A23,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P23" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C23,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q23" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D23,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R23" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E23,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;</v>
+      </c>
+      <c r="S23" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F23,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T23" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G23,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U23" t="str">
+        <f>IF(H23&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H23,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H164.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V23" t="str">
+        <f>IF(I23&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I23,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <f>IF(J23&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J23,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <f>IF(K23&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K23,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>527</v>
+      </c>
+      <c r="B24" s="24">
+        <v>5</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="N24" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A24,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;</v>
+      </c>
+      <c r="O24" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P24" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C24,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q24" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D24,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R24" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E24,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;</v>
+      </c>
+      <c r="S24" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F24,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T24" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G24,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U24" t="str">
+        <f>IF(H24&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H24,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H183.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V24" t="str">
+        <f>IF(I24&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I24,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f>IF(J24&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J24,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <f>IF(K24&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K24,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B25" s="24">
+        <v>5</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" t="s">
+        <v>315</v>
+      </c>
+      <c r="N25" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A25,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P25" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C25,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q25" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D25,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R25" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E25,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;</v>
+      </c>
+      <c r="S25" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F25,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T25" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G25,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U25" t="str">
+        <f>IF(H25&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H25,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H182.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V25" t="str">
+        <f>IF(I25&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I25,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <f>IF(J25&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J25,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <f>IF(K25&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K25,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B26" s="24">
+        <v>5</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" t="s">
+        <v>340</v>
+      </c>
+      <c r="N26" t="str">
+        <f>CONCATENATE("&lt;",A$1,"&gt;",A26,"&lt;/",A$1,"&gt;")</f>
+        <v>&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;duration&gt;5&lt;/duration&gt;</v>
+      </c>
+      <c r="P26" t="str">
+        <f>CONCATENATE("&lt;",C$1,"&gt;",C26,"&lt;/",C$1,"&gt;")</f>
+        <v>&lt;type&gt;&lt;/type&gt;</v>
+      </c>
+      <c r="Q26" t="str">
+        <f>CONCATENATE("&lt;",D$1,"&gt;",D26,"&lt;/",D$1,"&gt;")</f>
+        <v>&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;</v>
+      </c>
+      <c r="R26" t="str">
+        <f>CONCATENATE("&lt;",E$1,"&gt;",E26,"&lt;/",E$1,"&gt;")</f>
+        <v>&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;</v>
+      </c>
+      <c r="S26" t="str">
+        <f>CONCATENATE("&lt;",F$1,"&gt;",F26,"&lt;/",F$1,"&gt;")</f>
+        <v>&lt;changeFrom&gt;&lt;/changeFrom&gt;</v>
+      </c>
+      <c r="T26" t="str">
+        <f>CONCATENATE("&lt;",G$1,"&gt;",G26,"&lt;/",G$1,"&gt;")</f>
+        <v>&lt;changeTo&gt;&lt;/changeTo&gt;</v>
+      </c>
+      <c r="U26" t="str">
+        <f>IF(H26&lt;&gt;"",CONCATENATE("&lt;",H$1,"&gt;",H26,".mp3","&lt;/",H$1,"&gt;"),"")</f>
+        <v>&lt;mp3&gt;H201.mp3&lt;/mp3&gt;</v>
+      </c>
+      <c r="V26" t="str">
+        <f>IF(I26&lt;&gt;"",CONCATENATE("&lt;",I$1,"&gt;",I26,".mp3","&lt;/",I$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <f>IF(J26&lt;&gt;"",CONCATENATE("&lt;",J$1,"&gt;",J26,".mp3","&lt;/",J$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <f>IF(K26&lt;&gt;"",CONCATENATE("&lt;",K$1,"&gt;",K26,".mp3","&lt;/",K$1,"&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <f t="shared" si="8"/>
+        <v>&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:F2">
-    <cfRule type="duplicateValues" dxfId="19" priority="15" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E20:G20">
+    <cfRule type="duplicateValues" dxfId="18" priority="15" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:F3">
-    <cfRule type="duplicateValues" dxfId="18" priority="14" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E3:G3">
+    <cfRule type="duplicateValues" dxfId="17" priority="14" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:F4">
-    <cfRule type="duplicateValues" dxfId="17" priority="13" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E21:G21">
+    <cfRule type="duplicateValues" dxfId="16" priority="13" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:F5">
-    <cfRule type="duplicateValues" dxfId="16" priority="12" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E2:G2">
+    <cfRule type="duplicateValues" dxfId="15" priority="12" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:F6">
-    <cfRule type="duplicateValues" dxfId="15" priority="16" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E22:G22">
+    <cfRule type="duplicateValues" dxfId="14" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F7">
-    <cfRule type="duplicateValues" dxfId="14" priority="3" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E23:G23">
+    <cfRule type="duplicateValues" dxfId="13" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:F8">
-    <cfRule type="duplicateValues" dxfId="13" priority="6" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:F9">
+  <conditionalFormatting sqref="E4:G4">
     <cfRule type="duplicateValues" dxfId="12" priority="5" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D10:F10">
+  <conditionalFormatting sqref="E24:G24">
     <cfRule type="duplicateValues" dxfId="11" priority="11" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D11:F11">
+  <conditionalFormatting sqref="E25:G25">
     <cfRule type="duplicateValues" dxfId="10" priority="10" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12:F12">
+  <conditionalFormatting sqref="E26:G26">
     <cfRule type="duplicateValues" dxfId="9" priority="9" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:F13">
-    <cfRule type="duplicateValues" dxfId="8" priority="2" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E7:G7">
+    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14:F14">
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E6:G6">
+    <cfRule type="duplicateValues" dxfId="7" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:F15">
-    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E5:G5">
+    <cfRule type="duplicateValues" dxfId="6" priority="123" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:F16">
-    <cfRule type="duplicateValues" dxfId="5" priority="4" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E12:G12">
+    <cfRule type="duplicateValues" dxfId="5" priority="124" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:F17">
-    <cfRule type="duplicateValues" dxfId="4" priority="1" stopIfTrue="1"/>
+  <conditionalFormatting sqref="E8:G9 E11:G11 F10:G10">
+    <cfRule type="duplicateValues" dxfId="4" priority="125" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -5426,35 +6213,73 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="str">
-        <f>_xlfn.TEXTJOIN("",TRUE,"&lt;announcementList&gt;",slozit!W2:W88,"&lt;/announcementList&gt;")</f>
-        <v>&lt;announcementList&gt;&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Potraviny&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
+        <f>_xlfn.TEXTJOIN("",TRUE,"&lt;announcementList&gt;",slozit!Y:Y,"&lt;/announcementList&gt;")</f>
+        <v>&lt;announcementList&gt;&lt;announcement&gt;&lt;displayName&gt;Zavazadla&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
+zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zákaz jídla a pití &lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_NoFood&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že konzumace
 potravin není ve vozidlech povolena.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Nepokládat zavazadla&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Luggage&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#dc2828&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Upozorňujeme cestující, že pokládat
-zavazadla na sedadla není dovoleno.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not put your luggage on the seats.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H239.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Prostor pro invalidní vozík&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please do not eat any food in the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H340.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Kočárek&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
+místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Invalidní vozík&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_WheelChair&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
 místo pro invalidní vozík.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Prostor pro kočárek&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pram&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Uvolněte, prosím,
-místo pro kočárek.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a pram.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H240.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;Info&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vyčkáváme na vzájemný přestup&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Silná IAD, odklon&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please free the space for a wheelchair.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H260.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Postupujte dále do vozu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
+          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
+          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vyčkávání na čas odjezdu&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
+dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
+departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Bus&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na vzájemný přestup.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for a mutual transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H284.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vzájemný přestup (vlak)&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_SBahn&amp;quot;&amp;gt;~&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přestup z vlakové linky S dle stanovené čekací doby.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for an „S“ train transfer.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&amp;lt;/color&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;color bg=&amp;quot;#ffaa1e&amp;quot; fg=&amp;quot;#191919&amp;quot;&amp;gt;
 &amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#191919&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Z důvodu silné automobilové dopravy
 pojede tato linka odklonem.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
 &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;This line will be rerouted due to heavy traffic.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;
-&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H279.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Čas odjezdu dle JŘ&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Vyčkáváme na přesný čas odjezdu
-dle jízdního řádu.&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are waiting for the scheduled
-departure time.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H281.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;zpoždění IAD&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H279.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Letiště DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Air&amp;quot;&amp;gt;\&amp;lt;/icon&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Odlety&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Flight
+departures&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 1&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí mimo Schengenský prostor &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to countries outside the Schengen Area&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 2&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;lety do zemí Schengenského prostoru &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ flights to Schengen Area countries&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#9bcaea&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Terminál 3&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;40&amp;quot;&amp;gt;&amp;lt;b&amp;gt;pouze soukromé lety &amp;lt;/b&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;/ private flights only&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zpoždění&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Congestion&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;72&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Omlouváme
           se za zpoždění linky,
           které je zapříčiněno silnou individiální
           dopravou a špatnou průjezdností trasy&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
           &amp;lt;font size=&amp;quot;56&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;We are sorry for delay
           caused by heavy traffic and
-          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;postupte dále&lt;/displayName&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_GoFurther&amp;quot;&amp;gt;&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#d2d70f&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosíme,
-          postupujte dále do vozu.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-          &amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Please move further
-          into the vehicle.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H179.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
-&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;&lt;/announcementList&gt;</v>
+          limited passability of roads.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H280.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna pásma DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;FareZoneChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna tarifního pásma.&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Change of fare zone.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;6,8&lt;/changeFrom&gt;&lt;changeTo&gt;7&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;změna linky DEMO&lt;/displayName&gt;&lt;duration&gt;10&lt;/duration&gt;&lt;type&gt;LineChange&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Prosím pozor! Změna čísla linky&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;68&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please! Line number change.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;123&lt;/changeFrom&gt;&lt;changeTo&gt;XS2&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;zkrácený spoj DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;80&amp;quot;&amp;gt;Upozorňujeme cestující, že tento spoj končí v zastávce &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;60&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;Attention please, this bus terminates at &amp;lt;b&amp;gt;LETŇANY&amp;lt;/b&amp;gt;.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;  &lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;info o výluce DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font type=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#ffaa1e&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Koh-i-noor – Bělocerkevská&amp;lt;/b&amp;gt;&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font type=&amp;quot;48&amp;quot;&amp;gt;Vážení cestující, z důvodu opravy komunikace je linka v tomto úseku odkloněna po náhradní trase. Zastávky Kavkazská, Na Míčánkách a Bělocerkevská jsou vynechány.&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;trvalá změna DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Pid&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Změna linkového vedení BUS&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. září 2018&amp;lt;/b&amp;gt; dochází k trvalé změně linkového vedení
+autobusů PID &amp;lt;b&amp;gt;v oblasti Radotínska&amp;lt;/b&amp;gt;. Podrobnosti naleznete
+na zastávkách a na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;.&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;
+From saturday, &amp;lt;b&amp;gt;the 1st September 2018&amp;lt;/b&amp;gt;, several permanent changes and modifications
+will take place in operation of the PID system &amp;lt;b&amp;gt;in Radotín area&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more
+information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Jiné sdělení DEMO&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;&amp;lt;font size=&amp;quot;90&amp;quot;&amp;gt;&amp;lt;b&amp;gt;Zastávky na znamení od 1. 7. 2019&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;Od soboty &amp;lt;b&amp;gt;1. července 2019&amp;lt;/b&amp;gt; budou všechny autobusové zastávky
+na území hl. m. Prahy na znamení. Na autobus není nutné mávat,
+&amp;lt;b&amp;gt;stačí stát viditelně na zastávce&amp;lt;/b&amp;gt;. Před výstupem stiskněte
+s dostatečným předstihem &amp;lt;b&amp;gt;tlačítko STOP&amp;lt;/b&amp;gt; nebo tlačítko pro
+otevření dveří. Další informace naleznete na &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt;&amp;lt;/font&amp;gt;&amp;lt;br&amp;gt;
+&amp;lt;font size=&amp;quot;36&amp;quot;&amp;gt;&amp;lt;color fg=&amp;quot;#969696&amp;quot;&amp;gt;From saturday, the 1st July 2019, buses on all stops at Prague will stop on request only.
+You don‘t have lift a hand to stop the bus, &amp;lt;b&amp;gt;just stand in the bus stop area&amp;lt;/b&amp;gt;. Press the
+&amp;lt;b&amp;gt;STOP button or the door button&amp;lt;/b&amp;gt;. Visit &amp;lt;b&amp;gt;www.pid.cz&amp;lt;/b&amp;gt; for more information.&amp;lt;/color&amp;gt;&amp;lt;/font&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Zpráva z dispečinku DEMO&lt;/displayName&gt;&lt;duration&gt;15&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+    &amp;lt;icon type=&amp;quot;c_Exclamation&amp;quot;&amp;gt;!&amp;lt;/icon&amp;gt;
+&amp;lt;/color&amp;gt;    &lt;/icon&gt;&lt;text&gt;&amp;lt;color fg=&amp;quot;#ffffff&amp;quot; bg=&amp;quot;#c80014&amp;quot;&amp;gt;
+&amp;lt;font size=&amp;quot;48&amp;quot;&amp;gt;            
+    Z důvodu sněhové kalamity je ulice Horoměřická neprůjezdná.
+    Linky 316 a 356 jsou ze zastávky Statenice, Černý Vůl, hospoda
+    vedeny odklonem přes zastávky Výhledy, Zemědělská univerzita,
+    V Podbabě a Nádraží Podbaba do zastávky Dejvická (přestup
+    na metro „A“).&amp;lt;br&amp;gt;
+    Pravidelný povoz bude obnoven po zajištění sjízdnosti všech
+    komunikací (během dnešního odpoledne).
+&amp;lt;/font&amp;gt;
+&amp;lt;/color&amp;gt;&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Funkčnost klimatizace&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vážení cestující, pro správnou funkčnost klimatizace v tomto vozidle, která je nyní v provozu, prosíme neotevírejte boční okna ani stropní poklopy. Děkujeme Vám za pochopení.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H350.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Nastupujte předními dveřmi&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Prosíme, nastupujte předními dveřmi.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H205.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, linka ukončena&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Linka je z důvodu neprůjezdnosti trasy dočasně zkrácena.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H162.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Neprůjezdnost, odklon&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Diversion&amp;quot;&amp;gt;$&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Z důvodu neprůjezdnosti je linka vedena po odklonové trase.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H164.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Přední dveře, předložte doklad&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Nástup předními dveřmi. Předložte prosím jízdní doklad.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H183.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Uvolněte přední dveře&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Uvolněte prosím prostor předních dveří.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H182.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;announcement&gt;&lt;displayName&gt;Vozidlo obsazeno&lt;/displayName&gt;&lt;duration&gt;5&lt;/duration&gt;&lt;type&gt;&lt;/type&gt;&lt;icon&gt;&amp;lt;icon type=&amp;quot;c_Info&amp;quot;&amp;gt;[i]&amp;lt;/icon&amp;gt;&lt;/icon&gt;&lt;text&gt;Vozidlo plně obsazeno. Vyčkejte prosím na další spoj.&lt;/text&gt;&lt;changeFrom&gt;&lt;/changeFrom&gt;&lt;changeTo&gt;&lt;/changeTo&gt;&lt;mp3&gt;H201.mp3&lt;/mp3&gt;&lt;/announcement&gt;&lt;/announcementList&gt;</v>
       </c>
     </row>
   </sheetData>
@@ -5474,16 +6299,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="3" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -7174,122 +7999,122 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
